--- a/TP2026/TP6.xlsx
+++ b/TP2026/TP6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tahto\OneDrive\Documents\GitHub\u3\TP2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{874F14D4-9711-4120-8E76-ACB6FA64E73C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D258239-3C90-44F0-8EB7-0AD4F556257F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{AD6B512E-C032-4026-AB0F-DB211937A35A}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>الرقم</t>
   </si>
@@ -93,9 +93,6 @@
     <t>أعلى سعر  بعد التخفيض</t>
   </si>
   <si>
-    <t>معدل الأسعار</t>
-  </si>
-  <si>
     <t>N°</t>
   </si>
   <si>
@@ -151,13 +148,22 @@
   </si>
   <si>
     <t>Prix moyen</t>
+  </si>
+  <si>
+    <t>مجموع الأسعار بعد التخفيض</t>
+  </si>
+  <si>
+    <t>معدل الأسعار  بعد التخفيض</t>
+  </si>
+  <si>
+    <t>Total des prix sans réduction</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -168,12 +174,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Sakkal Majalla"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
       <color theme="1"/>
       <name val="Sakkal Majalla"/>
     </font>
@@ -198,7 +198,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -206,18 +206,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -241,22 +234,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>416169</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>193431</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>604944</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>1246</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1038237</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>145100</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="Image 10">
+        <xdr:cNvPr id="14" name="Image 13">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FA2047AC-5A9F-40D3-9790-CA520FE26767}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EDA8544F-4EE5-9FA3-466C-DB287BECB0CE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -272,17 +265,12 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6611815" y="492369"/>
-          <a:ext cx="4069114" cy="2340000"/>
+          <a:off x="7766050" y="730250"/>
+          <a:ext cx="3933837" cy="2520000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="accent5"/>
-          </a:solidFill>
-        </a:ln>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -294,23 +282,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>246187</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>193431</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>69850</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>596825</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>47215</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>386920</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="Image 10">
+        <xdr:cNvPr id="15" name="Image 14">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB2884AE-F611-4C9B-988C-A13505CC7661}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D4CD38A-879A-CB08-942D-553C3AE0DC89}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -326,17 +314,12 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6304087" y="490611"/>
-          <a:ext cx="4404478" cy="2785140"/>
+          <a:off x="6445250" y="228600"/>
+          <a:ext cx="5168470" cy="3352800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="accent5"/>
-          </a:solidFill>
-        </a:ln>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -661,221 +644,233 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2755BD4-5598-416E-B822-16FA80A762AD}">
-  <dimension ref="A1:O28"/>
+  <dimension ref="A1:N29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="31.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.33203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="23.6640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="18.5546875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="43.21875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="6.33203125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="11.5546875" style="1"/>
-    <col min="12" max="12" width="12.88671875" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="11.5546875" style="1"/>
+    <col min="2" max="2" width="40.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="43.21875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="6.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5546875" style="1"/>
+    <col min="11" max="11" width="12.88671875" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="11.5546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:14" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" s="4">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="4">
+        <v>5</v>
+      </c>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C3" s="4">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="1">
+      <c r="C4" s="4">
         <v>15</v>
       </c>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="K4" s="2"/>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="4">
+        <v>10</v>
+      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="1">
-        <v>10</v>
-      </c>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="4">
+        <v>8</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7" s="4">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C7" s="4">
+        <v>20</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8" s="4">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="4">
+        <v>7</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
         <v>8</v>
       </c>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" s="1">
-        <v>20</v>
-      </c>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A8" s="1">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
+      <c r="B9" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="1">
-        <v>7</v>
-      </c>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A9" s="1">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="4">
+        <v>6.5</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M10" s="3"/>
+      <c r="N10" s="2"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="D11" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="1">
-        <v>6.5</v>
-      </c>
-      <c r="N9" s="2"/>
-      <c r="O9" s="2"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="N10" s="4"/>
-      <c r="O10" s="2"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="D11" s="1" t="s">
+      <c r="E11" s="4"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="D12" s="4" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.5">
-      <c r="D12" s="1" t="s">
+      <c r="E12" s="4"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="D13" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E13" s="4"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="D14" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F12" s="5"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.5">
-      <c r="D13" s="1" t="s">
+      <c r="E14" s="4"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="D15" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F13" s="5"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.5">
-      <c r="D14" s="1" t="s">
+      <c r="E15" s="4"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="D16" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="F14" s="5"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.5">
-      <c r="D15" s="1" t="s">
+      <c r="E16" s="4"/>
+    </row>
+    <row r="17" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D17" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F15" s="5"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.5">
-      <c r="D16" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F16" s="5"/>
-    </row>
-    <row r="19" spans="6:7" x14ac:dyDescent="0.3">
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-    </row>
-    <row r="20" spans="6:7" x14ac:dyDescent="0.3">
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-    </row>
-    <row r="21" spans="6:7" x14ac:dyDescent="0.3">
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-    </row>
-    <row r="22" spans="6:7" x14ac:dyDescent="0.3">
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-    </row>
-    <row r="23" spans="6:7" x14ac:dyDescent="0.3">
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-    </row>
-    <row r="24" spans="6:7" x14ac:dyDescent="0.3">
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-    </row>
-    <row r="25" spans="6:7" x14ac:dyDescent="0.3">
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-    </row>
-    <row r="26" spans="6:7" x14ac:dyDescent="0.3">
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-    </row>
-    <row r="27" spans="6:7" x14ac:dyDescent="0.3">
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-    </row>
-    <row r="28" spans="6:7" x14ac:dyDescent="0.3">
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
+      <c r="E17" s="4"/>
+    </row>
+    <row r="20" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="F20" s="2"/>
+    </row>
+    <row r="21" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="F21" s="2"/>
+    </row>
+    <row r="22" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="F22" s="2"/>
+    </row>
+    <row r="23" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="F23" s="2"/>
+    </row>
+    <row r="24" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="F24" s="2"/>
+    </row>
+    <row r="25" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="F25" s="2"/>
+    </row>
+    <row r="26" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="F26" s="2"/>
+    </row>
+    <row r="27" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="F27" s="2"/>
+    </row>
+    <row r="28" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="F28" s="2"/>
+    </row>
+    <row r="29" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="F29" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -885,170 +880,157 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{026014EF-4694-4F35-AFE0-821F3283AFAE}">
-  <dimension ref="A1:J16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.21875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.5546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="20.77734375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.5546875" style="1"/>
-    <col min="7" max="7" width="12.88671875" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="11.5546875" style="1"/>
+    <col min="1" max="1" width="5.44140625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="23" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.44140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5546875" style="4"/>
+    <col min="7" max="7" width="12.88671875" style="4" customWidth="1"/>
+    <col min="8" max="16384" width="11.5546875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5" s="4" customFormat="1" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
+    <row r="2" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" s="4">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
+    <row r="3" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" s="4">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
+    <row r="4" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" s="4">
         <v>15</v>
       </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
+    </row>
+    <row r="5" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="4">
         <v>10</v>
       </c>
-      <c r="I5" s="6"/>
-      <c r="J5" s="2"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
+    </row>
+    <row r="6" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="4">
         <v>8</v>
       </c>
-      <c r="I6" s="6"/>
-      <c r="J6" s="2"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="1">
+    </row>
+    <row r="7" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="4">
         <v>6</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" s="4">
         <v>20</v>
       </c>
-      <c r="I7" s="6"/>
-      <c r="J7" s="2"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="1">
+    </row>
+    <row r="8" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="4">
         <v>7</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" s="4">
         <v>7</v>
       </c>
-      <c r="I8" s="6"/>
-      <c r="J8" s="2"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="1">
+    </row>
+    <row r="9" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
         <v>8</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" s="4">
         <v>6.5</v>
       </c>
-      <c r="I9" s="6"/>
-      <c r="J9" s="2"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="I10" s="7"/>
-      <c r="J10" s="2"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="D11" s="1" t="s">
+    </row>
+    <row r="11" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="D11" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="D12" s="1" t="s">
+    <row r="12" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="D12" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="D13" s="1" t="s">
+    <row r="13" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="D13" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="D14" s="1" t="s">
+    <row r="14" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="D14" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="D15" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="D15" s="1" t="s">
+    <row r="16" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="D16" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="D16" s="1" t="s">
-        <v>18</v>
+    <row r="17" spans="4:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="D17" s="4" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
